--- a/DataFiles/DetailsFileLive.xlsx
+++ b/DataFiles/DetailsFileLive.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="17925" windowHeight="9645"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="22935" windowHeight="9645"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
   <si>
     <t>Varibles</t>
   </si>
@@ -148,21 +148,12 @@
     <t>ADST06V3</t>
   </si>
   <si>
-    <t>St01M1</t>
-  </si>
-  <si>
     <t>ADST06M1</t>
   </si>
   <si>
-    <t>St01M2</t>
-  </si>
-  <si>
     <t>ADST06M2</t>
   </si>
   <si>
-    <t>St02M1</t>
-  </si>
-  <si>
     <t>ADSt07M1</t>
   </si>
   <si>
@@ -178,49 +169,133 @@
     <t>BG_Template alarm Escalate from st 07 to st 06</t>
   </si>
   <si>
-    <t>BG_AT by Atrribute_20.02.2026_060238</t>
-  </si>
-  <si>
-    <t>BG_Resource_20.02.2026_060238</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_20.02.2026_060238</t>
-  </si>
-  <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_21.02.2026_060238</t>
-  </si>
-  <si>
-    <t>BG-MA by attribute for extend-20.02.2026_072459</t>
-  </si>
-  <si>
-    <t>BG_AT by Atrribute_20.02.2026_102122</t>
-  </si>
-  <si>
-    <t>BG_Resource_20.02.2026_102122</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_20.02.2026_102122</t>
-  </si>
-  <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_21.02.2026_102122</t>
-  </si>
-  <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_21.02.2026_115242</t>
-  </si>
-  <si>
-    <t>BG-MA by attribute for extend-20.02.2026_124725</t>
-  </si>
-  <si>
-    <t>BG_AT by Atrribute_20.02.2026_124725</t>
-  </si>
-  <si>
-    <t>BG_Resource_20.02.2026_124725</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_20.02.2026_124725</t>
-  </si>
-  <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_21.02.2026_124725</t>
+    <t>SearWordForDelete</t>
+  </si>
+  <si>
+    <t>BG</t>
+  </si>
+  <si>
+    <t>BG_AT by</t>
+  </si>
+  <si>
+    <t>SearWordForDeleteTemplate</t>
+  </si>
+  <si>
+    <t>St01M01</t>
+  </si>
+  <si>
+    <t>St01M02</t>
+  </si>
+  <si>
+    <t>St02M01</t>
+  </si>
+  <si>
+    <t>newApiAlarmForMessage</t>
+  </si>
+  <si>
+    <t>BG- New APi ex st 06 from 07 LP</t>
+  </si>
+  <si>
+    <t>New APi St 06 esc</t>
+  </si>
+  <si>
+    <t>apiAlarmNameForEsclationAlarm</t>
+  </si>
+  <si>
+    <t>manualAlarmNameForEsclationAlarm</t>
+  </si>
+  <si>
+    <t>BG-MA by Esc resource MS</t>
+  </si>
+  <si>
+    <t>BG_AT by Atrribute_02.04.2026_064814</t>
+  </si>
+  <si>
+    <t>BG_Resource_02.04.2026_064814</t>
+  </si>
+  <si>
+    <t>BG_Escaltion Resource_02.04.2026_064814</t>
+  </si>
+  <si>
+    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_03.04.2026_064814</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-02.04.2026_074841</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-02.04.2026_134441</t>
+  </si>
+  <si>
+    <t>BG_AT by Atrribute_02.04.2026_134441</t>
+  </si>
+  <si>
+    <t>BG_Resource_02.04.2026_134441</t>
+  </si>
+  <si>
+    <t>BG_Escaltion Resource_02.04.2026_134441</t>
+  </si>
+  <si>
+    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_03.04.2026_134441</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-03.04.2026_064645</t>
+  </si>
+  <si>
+    <t>BG_AT by Atrribute_03.04.2026_064645</t>
+  </si>
+  <si>
+    <t>BG_Resource_03.04.2026_064645</t>
+  </si>
+  <si>
+    <t>BG_Escaltion Resource_03.04.2026_064645</t>
+  </si>
+  <si>
+    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_04.04.2026_064645</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-04.04.2026_091627</t>
+  </si>
+  <si>
+    <t>BG_AT by Atrribute_04.04.2026_091627</t>
+  </si>
+  <si>
+    <t>BG_Resource_04.04.2026_091627</t>
+  </si>
+  <si>
+    <t>BG_Escaltion Resource_04.04.2026_091627</t>
+  </si>
+  <si>
+    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_05.04.2026_091627</t>
+  </si>
+  <si>
+    <t>BG_AT by Atrribute_06.04.2026_064210</t>
+  </si>
+  <si>
+    <t>BG_Resource_06.04.2026_064210</t>
+  </si>
+  <si>
+    <t>BG_Escaltion Resource_06.04.2026_064210</t>
+  </si>
+  <si>
+    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_07.04.2026_064210</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-06.04.2026_072059</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-06.04.2026_080000</t>
+  </si>
+  <si>
+    <t>BG_AT by Atrribute_06.04.2026_080000</t>
+  </si>
+  <si>
+    <t>BG_Resource_06.04.2026_080000</t>
+  </si>
+  <si>
+    <t>BG_Escaltion Resource_06.04.2026_080000</t>
+  </si>
+  <si>
+    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_07.04.2026_080000</t>
   </si>
 </sst>
 </file>
@@ -228,7 +303,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -247,6 +322,12 @@
       <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF2A00FF"/>
+      <name val="Courier New"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -273,13 +354,14 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -575,12 +657,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="32.85546875"/>
     <col min="2" max="2" bestFit="true" customWidth="true" width="69.5703125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="46.0"/>
+    <col min="3" max="3" customWidth="true" hidden="true" width="46.0"/>
     <col min="4" max="4" bestFit="true" customWidth="true" width="52.140625"/>
     <col min="5" max="5" customWidth="true" width="38.7109375"/>
     <col min="6" max="6" bestFit="true" customWidth="true" width="47.140625"/>
@@ -756,12 +838,12 @@
     </row>
     <row r="21">
       <c r="B21" t="s" s="0">
-        <v>64</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="s" s="0">
-        <v>65</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -786,23 +868,23 @@
     </row>
     <row r="25">
       <c r="B25" t="s" s="0">
-        <v>66</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="B26" t="s" s="0">
         <v>43</v>
-      </c>
-      <c r="B26" t="s" s="0">
-        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s" s="0">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -811,36 +893,76 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s" s="0">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="s" s="0">
-        <v>67</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="s" s="0">
-        <v>63</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s" s="0">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B33" t="s" s="0">
         <v>51</v>
       </c>
-      <c r="B32" t="s" s="0">
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="B34" t="s" s="0">
         <v>52</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/DataFiles/DetailsFileLive.xlsx
+++ b/DataFiles/DetailsFileLive.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="169">
   <si>
     <t>Varibles</t>
   </si>
@@ -296,6 +296,234 @@
   </si>
   <si>
     <t>Bg_1 Day Information-Event by Fire fighter (two Station)_07.04.2026_080000</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-07.04.2026_080340</t>
+  </si>
+  <si>
+    <t>BG_AT by Atrribute_07.04.2026_080340</t>
+  </si>
+  <si>
+    <t>BG_Resource_07.04.2026_080340</t>
+  </si>
+  <si>
+    <t>BG_Escaltion Resource_07.04.2026_080340</t>
+  </si>
+  <si>
+    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_08.04.2026_080340</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-08.04.2026_083933</t>
+  </si>
+  <si>
+    <t>BG_AT by Atrribute_08.04.2026_083933</t>
+  </si>
+  <si>
+    <t>BG_Resource_08.04.2026_083933</t>
+  </si>
+  <si>
+    <t>BG_Escaltion Resource_08.04.2026_083933</t>
+  </si>
+  <si>
+    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_09.04.2026_083933</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-09.04.2026_063050</t>
+  </si>
+  <si>
+    <t>BG_AT by Atrribute_09.04.2026_063050</t>
+  </si>
+  <si>
+    <t>BG_Resource_09.04.2026_063050</t>
+  </si>
+  <si>
+    <t>BG_Escaltion Resource_09.04.2026_063050</t>
+  </si>
+  <si>
+    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_10.04.2026_063050</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-10.04.2026_070332</t>
+  </si>
+  <si>
+    <t>BG_AT by Atrribute_10.04.2026_070332</t>
+  </si>
+  <si>
+    <t>BG_Resource_10.04.2026_070332</t>
+  </si>
+  <si>
+    <t>BG_Escaltion Resource_10.04.2026_070332</t>
+  </si>
+  <si>
+    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_11.04.2026_070332</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-13.04.2026_065953</t>
+  </si>
+  <si>
+    <t>BG_AT by Atrribute_13.04.2026_065953</t>
+  </si>
+  <si>
+    <t>BG_Resource_13.04.2026_065953</t>
+  </si>
+  <si>
+    <t>BG_Escaltion Resource_13.04.2026_065953</t>
+  </si>
+  <si>
+    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_14.04.2026_065953</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-15.04.2026_064543</t>
+  </si>
+  <si>
+    <t>BG_AT by Atrribute_15.04.2026_064543</t>
+  </si>
+  <si>
+    <t>BG_Resource_15.04.2026_064543</t>
+  </si>
+  <si>
+    <t>BG_Escaltion Resource_15.04.2026_064543</t>
+  </si>
+  <si>
+    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_16.04.2026_064543</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-16.04.2026_064753</t>
+  </si>
+  <si>
+    <t>BG_AT by Atrribute_16.04.2026_064753</t>
+  </si>
+  <si>
+    <t>BG_Resource_16.04.2026_064753</t>
+  </si>
+  <si>
+    <t>BG_Escaltion Resource_16.04.2026_064753</t>
+  </si>
+  <si>
+    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_17.04.2026_064753</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-17.04.2026_064439</t>
+  </si>
+  <si>
+    <t>BG_AT by Atrribute_17.04.2026_064439</t>
+  </si>
+  <si>
+    <t>BG_Resource_17.04.2026_064439</t>
+  </si>
+  <si>
+    <t>BG_Escaltion Resource_17.04.2026_064439</t>
+  </si>
+  <si>
+    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_18.04.2026_064439</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-20.04.2026_075506</t>
+  </si>
+  <si>
+    <t>BG_AT by Atrribute_20.04.2026_075506</t>
+  </si>
+  <si>
+    <t>BG_Resource_20.04.2026_075506</t>
+  </si>
+  <si>
+    <t>BG_Escaltion Resource_20.04.2026_075506</t>
+  </si>
+  <si>
+    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_21.04.2026_075506</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-21.04.2026_064213</t>
+  </si>
+  <si>
+    <t>BG_AT by Atrribute_21.04.2026_064213</t>
+  </si>
+  <si>
+    <t>BG_Resource_21.04.2026_064213</t>
+  </si>
+  <si>
+    <t>BG_Escaltion Resource_21.04.2026_064213</t>
+  </si>
+  <si>
+    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_22.04.2026_064213</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-23.04.2026_064258</t>
+  </si>
+  <si>
+    <t>BG_AT by Atrribute_23.04.2026_064258</t>
+  </si>
+  <si>
+    <t>BG_Resource_23.04.2026_064258</t>
+  </si>
+  <si>
+    <t>BG_Escaltion Resource_23.04.2026_064258</t>
+  </si>
+  <si>
+    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_24.04.2026_064258</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-24.04.2026_065142</t>
+  </si>
+  <si>
+    <t>BG_AT by Atrribute_24.04.2026_065142</t>
+  </si>
+  <si>
+    <t>BG_Resource_24.04.2026_065142</t>
+  </si>
+  <si>
+    <t>BG_Escaltion Resource_24.04.2026_065142</t>
+  </si>
+  <si>
+    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_25.04.2026_065142</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-27.04.2026_070624</t>
+  </si>
+  <si>
+    <t>BG_AT by Atrribute_27.04.2026_070624</t>
+  </si>
+  <si>
+    <t>BG_Resource_27.04.2026_070624</t>
+  </si>
+  <si>
+    <t>BG_Escaltion Resource_27.04.2026_070624</t>
+  </si>
+  <si>
+    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_28.04.2026_070624</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-28.04.2026_065401</t>
+  </si>
+  <si>
+    <t>BG_AT by Atrribute_28.04.2026_065401</t>
+  </si>
+  <si>
+    <t>BG_Resource_28.04.2026_065401</t>
+  </si>
+  <si>
+    <t>BG_Escaltion Resource_28.04.2026_065401</t>
+  </si>
+  <si>
+    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_29.04.2026_065401</t>
+  </si>
+  <si>
+    <t>BG_Escaltion Resource_28.04.2026_083715</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-28.04.2026_085630</t>
+  </si>
+  <si>
+    <t>BG_AT by Atrribute_28.04.2026_085630</t>
+  </si>
+  <si>
+    <t>BG_Resource_28.04.2026_085630</t>
+  </si>
+  <si>
+    <t>BG_Escaltion Resource_28.04.2026_085630</t>
+  </si>
+  <si>
+    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_29.04.2026_085630</t>
   </si>
 </sst>
 </file>
@@ -838,12 +1066,12 @@
     </row>
     <row r="21">
       <c r="B21" t="s" s="0">
-        <v>89</v>
+        <v>165</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="s" s="0">
-        <v>90</v>
+        <v>166</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -868,7 +1096,7 @@
     </row>
     <row r="25">
       <c r="B25" t="s" s="0">
-        <v>91</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -901,12 +1129,12 @@
     </row>
     <row r="29">
       <c r="B29" t="s" s="0">
-        <v>92</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="s" s="0">
-        <v>88</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31" spans="1:7">

--- a/DataFiles/DetailsFileLive.xlsx
+++ b/DataFiles/DetailsFileLive.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="22935" windowHeight="9645"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="22605" windowHeight="9645"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <si>
     <t>Varibles</t>
   </si>
@@ -208,322 +208,76 @@
     <t>BG-MA by Esc resource MS</t>
   </si>
   <si>
-    <t>BG_AT by Atrribute_02.04.2026_064814</t>
-  </si>
-  <si>
-    <t>BG_Resource_02.04.2026_064814</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_02.04.2026_064814</t>
-  </si>
-  <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_03.04.2026_064814</t>
-  </si>
-  <si>
-    <t>BG-MA by attribute for extend-02.04.2026_074841</t>
-  </si>
-  <si>
-    <t>BG-MA by attribute for extend-02.04.2026_134441</t>
-  </si>
-  <si>
-    <t>BG_AT by Atrribute_02.04.2026_134441</t>
-  </si>
-  <si>
-    <t>BG_Resource_02.04.2026_134441</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_02.04.2026_134441</t>
-  </si>
-  <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_03.04.2026_134441</t>
-  </si>
-  <si>
-    <t>BG-MA by attribute for extend-03.04.2026_064645</t>
-  </si>
-  <si>
-    <t>BG_AT by Atrribute_03.04.2026_064645</t>
-  </si>
-  <si>
-    <t>BG_Resource_03.04.2026_064645</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_03.04.2026_064645</t>
-  </si>
-  <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_04.04.2026_064645</t>
-  </si>
-  <si>
-    <t>BG-MA by attribute for extend-04.04.2026_091627</t>
-  </si>
-  <si>
-    <t>BG_AT by Atrribute_04.04.2026_091627</t>
-  </si>
-  <si>
-    <t>BG_Resource_04.04.2026_091627</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_04.04.2026_091627</t>
-  </si>
-  <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_05.04.2026_091627</t>
-  </si>
-  <si>
-    <t>BG_AT by Atrribute_06.04.2026_064210</t>
-  </si>
-  <si>
-    <t>BG_Resource_06.04.2026_064210</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_06.04.2026_064210</t>
-  </si>
-  <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_07.04.2026_064210</t>
-  </si>
-  <si>
-    <t>BG-MA by attribute for extend-06.04.2026_072059</t>
-  </si>
-  <si>
-    <t>BG-MA by attribute for extend-06.04.2026_080000</t>
-  </si>
-  <si>
-    <t>BG_AT by Atrribute_06.04.2026_080000</t>
-  </si>
-  <si>
-    <t>BG_Resource_06.04.2026_080000</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_06.04.2026_080000</t>
-  </si>
-  <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_07.04.2026_080000</t>
-  </si>
-  <si>
-    <t>BG-MA by attribute for extend-07.04.2026_080340</t>
-  </si>
-  <si>
-    <t>BG_AT by Atrribute_07.04.2026_080340</t>
-  </si>
-  <si>
-    <t>BG_Resource_07.04.2026_080340</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_07.04.2026_080340</t>
-  </si>
-  <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_08.04.2026_080340</t>
-  </si>
-  <si>
-    <t>BG-MA by attribute for extend-08.04.2026_083933</t>
-  </si>
-  <si>
-    <t>BG_AT by Atrribute_08.04.2026_083933</t>
-  </si>
-  <si>
-    <t>BG_Resource_08.04.2026_083933</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_08.04.2026_083933</t>
-  </si>
-  <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_09.04.2026_083933</t>
-  </si>
-  <si>
-    <t>BG-MA by attribute for extend-09.04.2026_063050</t>
-  </si>
-  <si>
-    <t>BG_AT by Atrribute_09.04.2026_063050</t>
-  </si>
-  <si>
-    <t>BG_Resource_09.04.2026_063050</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_09.04.2026_063050</t>
-  </si>
-  <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_10.04.2026_063050</t>
-  </si>
-  <si>
-    <t>BG-MA by attribute for extend-10.04.2026_070332</t>
-  </si>
-  <si>
-    <t>BG_AT by Atrribute_10.04.2026_070332</t>
-  </si>
-  <si>
-    <t>BG_Resource_10.04.2026_070332</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_10.04.2026_070332</t>
-  </si>
-  <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_11.04.2026_070332</t>
-  </si>
-  <si>
-    <t>BG-MA by attribute for extend-13.04.2026_065953</t>
-  </si>
-  <si>
-    <t>BG_AT by Atrribute_13.04.2026_065953</t>
-  </si>
-  <si>
-    <t>BG_Resource_13.04.2026_065953</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_13.04.2026_065953</t>
-  </si>
-  <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_14.04.2026_065953</t>
-  </si>
-  <si>
-    <t>BG-MA by attribute for extend-15.04.2026_064543</t>
-  </si>
-  <si>
-    <t>BG_AT by Atrribute_15.04.2026_064543</t>
-  </si>
-  <si>
-    <t>BG_Resource_15.04.2026_064543</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_15.04.2026_064543</t>
-  </si>
-  <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_16.04.2026_064543</t>
-  </si>
-  <si>
-    <t>BG-MA by attribute for extend-16.04.2026_064753</t>
-  </si>
-  <si>
-    <t>BG_AT by Atrribute_16.04.2026_064753</t>
-  </si>
-  <si>
-    <t>BG_Resource_16.04.2026_064753</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_16.04.2026_064753</t>
-  </si>
-  <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_17.04.2026_064753</t>
-  </si>
-  <si>
-    <t>BG-MA by attribute for extend-17.04.2026_064439</t>
-  </si>
-  <si>
-    <t>BG_AT by Atrribute_17.04.2026_064439</t>
-  </si>
-  <si>
-    <t>BG_Resource_17.04.2026_064439</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_17.04.2026_064439</t>
-  </si>
-  <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_18.04.2026_064439</t>
-  </si>
-  <si>
-    <t>BG-MA by attribute for extend-20.04.2026_075506</t>
-  </si>
-  <si>
-    <t>BG_AT by Atrribute_20.04.2026_075506</t>
-  </si>
-  <si>
-    <t>BG_Resource_20.04.2026_075506</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_20.04.2026_075506</t>
-  </si>
-  <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_21.04.2026_075506</t>
-  </si>
-  <si>
-    <t>BG-MA by attribute for extend-21.04.2026_064213</t>
-  </si>
-  <si>
-    <t>BG_AT by Atrribute_21.04.2026_064213</t>
-  </si>
-  <si>
-    <t>BG_Resource_21.04.2026_064213</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_21.04.2026_064213</t>
-  </si>
-  <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_22.04.2026_064213</t>
-  </si>
-  <si>
-    <t>BG-MA by attribute for extend-23.04.2026_064258</t>
-  </si>
-  <si>
-    <t>BG_AT by Atrribute_23.04.2026_064258</t>
-  </si>
-  <si>
-    <t>BG_Resource_23.04.2026_064258</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_23.04.2026_064258</t>
-  </si>
-  <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_24.04.2026_064258</t>
-  </si>
-  <si>
-    <t>BG-MA by attribute for extend-24.04.2026_065142</t>
-  </si>
-  <si>
-    <t>BG_AT by Atrribute_24.04.2026_065142</t>
-  </si>
-  <si>
-    <t>BG_Resource_24.04.2026_065142</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_24.04.2026_065142</t>
-  </si>
-  <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_25.04.2026_065142</t>
-  </si>
-  <si>
-    <t>BG-MA by attribute for extend-27.04.2026_070624</t>
-  </si>
-  <si>
-    <t>BG_AT by Atrribute_27.04.2026_070624</t>
-  </si>
-  <si>
-    <t>BG_Resource_27.04.2026_070624</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_27.04.2026_070624</t>
-  </si>
-  <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_28.04.2026_070624</t>
-  </si>
-  <si>
-    <t>BG-MA by attribute for extend-28.04.2026_065401</t>
-  </si>
-  <si>
-    <t>BG_AT by Atrribute_28.04.2026_065401</t>
-  </si>
-  <si>
-    <t>BG_Resource_28.04.2026_065401</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_28.04.2026_065401</t>
-  </si>
-  <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_29.04.2026_065401</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_28.04.2026_083715</t>
-  </si>
-  <si>
-    <t>BG-MA by attribute for extend-28.04.2026_085630</t>
-  </si>
-  <si>
-    <t>BG_AT by Atrribute_28.04.2026_085630</t>
-  </si>
-  <si>
-    <t>BG_Resource_28.04.2026_085630</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_28.04.2026_085630</t>
-  </si>
-  <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_29.04.2026_085630</t>
+    <t>st01FFEmailCallSms</t>
+  </si>
+  <si>
+    <t>Jonas4 Jonas04</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-05.05.2026_094445</t>
+  </si>
+  <si>
+    <t>BG_AT by Atrribute_05.05.2026_094445</t>
+  </si>
+  <si>
+    <t>BG_Resource_05.05.2026_094445</t>
+  </si>
+  <si>
+    <t>BG_Escaltion Resource_05.05.2026_094445</t>
+  </si>
+  <si>
+    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_06.05.2026_094445</t>
+  </si>
+  <si>
+    <t>sff</t>
+  </si>
+  <si>
+    <t>st01Al1</t>
+  </si>
+  <si>
+    <t>st02Al1</t>
+  </si>
+  <si>
+    <t>ADSt06Al2</t>
+  </si>
+  <si>
+    <t>ADSt07Al2</t>
+  </si>
+  <si>
+    <t>BG-chatGroupByFireFighter06.05.2026_100740</t>
+  </si>
+  <si>
+    <t>BG-chatGroupByResource06.05.2026_100740</t>
+  </si>
+  <si>
+    <t>BG-chatGroupByAttribute06.05.2026_100740</t>
+  </si>
+  <si>
+    <t>BG-chatGroupByAlarmLoops06.05.2026_101751</t>
+  </si>
+  <si>
+    <t>BG-chatGroupByFireFighter06.05.2026_101946</t>
+  </si>
+  <si>
+    <t>BG-chatGroupByAlarmLoops06.05.2026_101946</t>
+  </si>
+  <si>
+    <t>BG-chatGroupByResource06.05.2026_101946</t>
+  </si>
+  <si>
+    <t>BG-chatGroupByAttribute06.05.2026_101946</t>
+  </si>
+  <si>
+    <t>BG-chatGroupByAttribute06.05.2026_145024</t>
+  </si>
+  <si>
+    <t>BG-chatGroupByResource06.05.2026_145024</t>
+  </si>
+  <si>
+    <t>BG-chatGroupByAlarmLoops06.05.2026_145024</t>
+  </si>
+  <si>
+    <t>BG-chatGroupByFireFighter06.05.2026_145024</t>
   </si>
 </sst>
 </file>
@@ -531,7 +285,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -554,6 +308,12 @@
     <font>
       <sz val="10"/>
       <color rgb="FF2A00FF"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0000C0"/>
       <name val="Courier New"/>
       <family val="3"/>
     </font>
@@ -582,7 +342,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
@@ -590,6 +350,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -885,10 +646,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="32.85546875"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="36.5703125"/>
     <col min="2" max="2" bestFit="true" customWidth="true" width="69.5703125"/>
     <col min="3" max="3" customWidth="true" hidden="true" width="46.0"/>
     <col min="4" max="4" bestFit="true" customWidth="true" width="52.140625"/>
@@ -1064,14 +825,14 @@
       </c>
       <c r="F20" s="2"/>
     </row>
-    <row r="21">
+    <row r="21" spans="1:7">
       <c r="B21" t="s" s="0">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="B22" t="s" s="0">
-        <v>166</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1094,9 +855,9 @@
       <c r="D24" s="2"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:7">
       <c r="B25" t="s" s="0">
-        <v>167</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1127,14 +888,14 @@
         <v>45</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:7">
       <c r="B29" t="s" s="0">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="B30" t="s" s="0">
-        <v>164</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1191,6 +952,50 @@
       </c>
       <c r="B37" s="4" t="s">
         <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="s" s="0">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="s" s="0">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="s" s="0">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="15.75">
+      <c r="A43" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15.75">
+      <c r="A44" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
